--- a/panchang-data/Bhimashankar_Asam2026.xlsx
+++ b/panchang-data/Bhimashankar_Asam2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5389">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16192,6 +16192,9 @@
   </si>
   <si>
     <t>121°05'11.55</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16681,7 +16684,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16767,7 +16770,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -16853,7 +16856,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16939,7 +16942,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>89</v>
@@ -17025,7 +17028,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17111,7 +17114,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>125</v>
@@ -17197,7 +17200,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>143</v>
@@ -17283,7 +17286,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17369,7 +17372,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>50</v>
@@ -17455,7 +17458,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17541,7 +17544,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>89</v>
@@ -17627,7 +17630,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17713,7 +17716,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>125</v>
@@ -17799,7 +17802,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>143</v>
@@ -17885,7 +17888,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -17971,7 +17974,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>50</v>
@@ -18057,7 +18060,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18143,7 +18146,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>89</v>
@@ -18229,7 +18232,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18315,7 +18318,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>125</v>
@@ -18401,7 +18404,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>143</v>
@@ -18487,7 +18490,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18573,7 +18576,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -18659,7 +18662,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18745,7 +18748,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>89</v>
@@ -18831,7 +18834,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18917,7 +18920,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>125</v>
@@ -19003,7 +19006,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>143</v>
@@ -19089,7 +19092,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19175,7 +19178,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>50</v>
@@ -19261,7 +19264,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19347,7 +19350,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>88</v>
+        <v>559</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>89</v>
@@ -19433,7 +19436,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19519,7 +19522,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>125</v>
@@ -19605,7 +19608,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>143</v>
@@ -19691,7 +19694,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19777,7 +19780,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
@@ -19863,7 +19866,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -19949,7 +19952,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>89</v>
@@ -20035,7 +20038,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20121,7 +20124,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>125</v>
@@ -20207,7 +20210,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>143</v>
@@ -20293,7 +20296,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20379,7 +20382,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>50</v>
@@ -20465,7 +20468,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20551,7 +20554,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>89</v>
@@ -20637,7 +20640,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20723,7 +20726,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>125</v>
@@ -20809,7 +20812,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>143</v>
@@ -20895,7 +20898,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -20981,7 +20984,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>50</v>
@@ -21067,7 +21070,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21153,7 +21156,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>89</v>
@@ -21239,7 +21242,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21325,7 +21328,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>125</v>
@@ -21411,7 +21414,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>143</v>
@@ -21497,7 +21500,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21583,7 +21586,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -21669,7 +21672,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21755,7 +21758,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>89</v>
@@ -21841,7 +21844,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21927,7 +21930,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>559</v>
+        <v>999</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>125</v>
@@ -22013,7 +22016,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>143</v>
@@ -22099,7 +22102,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22185,7 +22188,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
@@ -22271,7 +22274,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22357,7 +22360,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>89</v>
@@ -22443,7 +22446,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22529,7 +22532,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>125</v>
@@ -22615,7 +22618,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>143</v>
@@ -22701,7 +22704,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22787,7 +22790,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>50</v>
@@ -22873,7 +22876,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -22959,7 +22962,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>89</v>
@@ -23045,7 +23048,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23131,7 +23134,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>125</v>
@@ -23217,7 +23220,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>143</v>
@@ -23303,7 +23306,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23389,7 +23392,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>50</v>
@@ -23475,7 +23478,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23561,7 +23564,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>89</v>
@@ -23647,7 +23650,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23733,7 +23736,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>125</v>
@@ -23819,7 +23822,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>143</v>
@@ -23905,7 +23908,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -23991,7 +23994,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>50</v>
@@ -24077,7 +24080,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24163,7 +24166,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>89</v>
@@ -24249,7 +24252,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24335,7 +24338,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>125</v>
@@ -24421,7 +24424,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>143</v>
@@ -24507,7 +24510,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>999</v>
+        <v>1438</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24593,7 +24596,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>50</v>
@@ -24679,7 +24682,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24765,7 +24768,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>89</v>
@@ -24851,7 +24854,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24937,7 +24940,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>125</v>
@@ -25023,7 +25026,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>143</v>
@@ -25109,7 +25112,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25195,7 +25198,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>50</v>
@@ -25281,7 +25284,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25367,7 +25370,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>89</v>
@@ -25453,7 +25456,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25539,7 +25542,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>125</v>
@@ -25625,7 +25628,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>143</v>
@@ -25711,7 +25714,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25797,7 +25800,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>50</v>
@@ -25883,7 +25886,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -25969,7 +25972,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>89</v>
@@ -26055,7 +26058,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26141,7 +26144,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>125</v>
@@ -26227,7 +26230,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>143</v>
@@ -26313,7 +26316,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26399,7 +26402,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>50</v>
@@ -26485,7 +26488,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26571,7 +26574,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>89</v>
@@ -26657,7 +26660,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26743,7 +26746,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>125</v>
@@ -26829,7 +26832,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>143</v>
@@ -26915,7 +26918,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27001,7 +27004,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1438</v>
+        <v>1861</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>50</v>
@@ -27087,7 +27090,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1861</v>
+        <v>2296</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27173,7 +27176,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1861</v>
+        <v>2296</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>89</v>
@@ -27259,7 +27262,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1861</v>
+        <v>2296</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27345,7 +27348,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1861</v>
+        <v>2296</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>125</v>
@@ -27431,7 +27434,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1861</v>
+        <v>2296</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>143</v>
@@ -27517,7 +27520,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1861</v>
+        <v>2296</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27603,7 +27606,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1861</v>
+        <v>2296</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>50</v>
@@ -27689,7 +27692,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1861</v>
+        <v>2296</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27775,7 +27778,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1861</v>
+        <v>2296</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>89</v>
@@ -27861,7 +27864,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1861</v>
+        <v>2296</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27947,7 +27950,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1861</v>
+        <v>2296</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>125</v>
@@ -28033,7 +28036,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1861</v>
+        <v>2296</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>143</v>
@@ -28119,7 +28122,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1861</v>
+        <v>2296</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28205,7 +28208,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1861</v>
+        <v>2296</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>50</v>
@@ -28291,7 +28294,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1861</v>
+        <v>2296</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28377,7 +28380,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1861</v>
+        <v>5388</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>89</v>
@@ -28463,7 +28466,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1861</v>
+        <v>5388</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28549,7 +28552,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1861</v>
+        <v>5388</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>125</v>
@@ -28635,7 +28638,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1861</v>
+        <v>5388</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>143</v>
@@ -28721,7 +28724,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1861</v>
+        <v>5388</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28807,7 +28810,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1861</v>
+        <v>5388</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>50</v>
@@ -28893,7 +28896,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1861</v>
+        <v>5388</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -28979,7 +28982,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1861</v>
+        <v>5388</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>89</v>
@@ -29065,7 +29068,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1861</v>
+        <v>5388</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29151,7 +29154,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1861</v>
+        <v>5388</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>125</v>
@@ -29237,7 +29240,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1861</v>
+        <v>5388</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>143</v>
@@ -29323,7 +29326,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1861</v>
+        <v>5388</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29409,7 +29412,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1861</v>
+        <v>5388</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -29495,7 +29498,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1861</v>
+        <v>5388</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29581,7 +29584,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1861</v>
+        <v>5388</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>89</v>
@@ -29667,7 +29670,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2296</v>
+        <v>5388</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29753,7 +29756,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2296</v>
+        <v>5388</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>125</v>
@@ -29839,7 +29842,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2296</v>
+        <v>5388</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>143</v>
@@ -29925,7 +29928,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2296</v>
+        <v>5388</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30011,7 +30014,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2296</v>
+        <v>5388</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>50</v>
@@ -30097,7 +30100,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2296</v>
+        <v>5388</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30183,7 +30186,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2296</v>
+        <v>5388</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>89</v>
@@ -30269,7 +30272,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2296</v>
+        <v>5388</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30355,7 +30358,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2296</v>
+        <v>5388</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>125</v>
@@ -30441,7 +30444,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2296</v>
+        <v>5388</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>143</v>
@@ -30527,7 +30530,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2296</v>
+        <v>5388</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30613,7 +30616,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2296</v>
+        <v>5388</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>50</v>
@@ -30699,7 +30702,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2296</v>
+        <v>5388</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30785,7 +30788,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2296</v>
+        <v>5388</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>89</v>
@@ -30871,7 +30874,7 @@
         <v>46188</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>2296</v>
+        <v>5388</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
